--- a/resultados/telemacoborba/inventario_externos.xlsx
+++ b/resultados/telemacoborba/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6945,6 +6945,332 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>http://www.pmtb.pr.gov.br/noticia.php?codigo=7191</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>www.pmtb.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/13306-hemonucleo-de-telemaco-borba-e-inaugurado-e-atende-a-7-municipios</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>5</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:58:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>http://www.pmtb.pr.gov.br/noticia.php?codigo=6948</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>www.pmtb.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/12669-ubs-do-bandeirantes-realiza-primeiro-encontro-do-grupo-de-saude-mental</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>5</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:59:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>http://www.pmtb.pr.gov.br/noticia.php?codigo=6858</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>www.pmtb.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/12457-secretaria-de-saude-realiza-palestra-sobre-laqueadura</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>5</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:00:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>http://www.pmtb.pr.gov.br/noticia.php?codigo=6835</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>www.pmtb.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/12422-prestacao-de-contas-do-transporte-escolar-sera-tema-da-reuniao-do-conselho-do-fundeb</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>5</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:01:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>http://www.pmtb.pr.gov.br/noticia.php?codigo=6819</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>www.pmtb.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/12385-sms-realiza-exames-preventivos-no-sabado-14-na-area-2</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>5</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:02:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>http://www.pmtb.pr.gov.br/noticia.php?codigo=6796</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>www.pmtb.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/12335-telemaco-borba-aplica-r-11-8-milhoes-em-saude-no-1-quadrimestre-de-2014</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>5</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:02:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>http://www.viniciusdemoraes.com.br/pt-br/poesia/poesias-avulsas/casa</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>www.viniciusdemoraes.com.br</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>http://www.viniciusdemoraes.com.br/pt-br/poesia/poesias-avulsas/casa</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/educacao/blog-da-educacao/8240-vivencias-a-casa-vinicius-de-moraes</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>5</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:06:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1siu20NA4OU</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1siu20NA4OU</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/19976-saude-realiza-audiencia-publica-e-prestacao-de-contas-de-2023</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>5</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://sbim.org.br/images/files/po-avaaz-relatorio-antivacina.pdf</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sbim.org.br</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://sbim.org.br/images/files/po-avaaz-relatorio-antivacina.pdf</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18943-recebeu-mensagem-sobre-saude-nao-compartilhe-antes-de-checar</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>5</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>http://www.paralisiainfantil.com.br</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>www.paralisiainfantil.com.br</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>www.paralisiainfantil.com.br</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/17029-campanha-de-vacinacao-contra-polio-e-multivacinacao-e-prorrogada-ate-dia-30</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>5</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:16:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/telemacoborba/inventario_externos.xlsx
+++ b/resultados/telemacoborba/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7271,6 +7271,632 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>http://drauziovarella.com.br/corpo-humano/faringe/</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>drauziovarella.com.br</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>faringe</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/16196-saude-alerta-para-o-aumento-dos-casos-da-sindrome-mao-pe-boca</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>5</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://pebmed.com.br/coronavirus-tudo-o-que-voce-precisa-saber-sobre-a-nova-pandemia/</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>pebmed.com.br</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>diagnóstico da Covid-19</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/9083-vacinacao-contra-influenza-comeca-por-idosos-e-profissionais-de-saude</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>5</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:31:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Wyms5B84UbdA5dn39</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://forms.gle/Wyms5B84UbdA5dn39</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/20472-inca-promove-evento-on-line-para-comunicacao-e-mobilizacao-social-no-controle-de-canceres</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>6</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:05:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>http://congresso.redecidadedigital.com.br/</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>congresso.redecidadedigital.com.br</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>http://congresso.redecidadedigital.com.br/</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/13782-populacao-podera-agendar-consulta-medica-via-internet</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>6</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:12:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/media/set/?set=a.669814301841052&amp;type=3</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18922-sms-forma-10-agentes-de-saude-no-programa-saude-com-agente</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>6</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:14:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.sbd.org.br/janeiroroxo/</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>www.sbd.org.br</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://www.sbd.org.br/janeiroroxo/</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/17710-dia-nacional-de-combate-e-prevencao-da-hanseniase-alerta-para-sinais-e-sintomas-da-doenca</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>6</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:19:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/e-nota/verificar_autenticidade_direct.faces?p1=5EgYIL1kjUM=&amp;p2=0G6jwHpOtUA=</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Para NFS-e emitidas ATÉ 30/04/2016, clique aqui.</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/transito/21-servicos/nota-fiscal-eletronica</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>7</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-08-05 18:47:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>http://www.marinha.mil.br</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>www.marinha.mil.br</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>www.marinha.mil.br</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/5236-secretaria-de-saude-destaca-o-agosto-dourado-com-incentivo-ao-aleitamento-materno</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>7</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-08-05 18:55:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PrefeituraTelemacoBorba</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude?start=1190</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>7</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-08-05 18:55:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?q=Rua+Rodrigues+Alves,+n%C2%BA+95&amp;entry=gmail&amp;source=g</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>maps.google.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Rua Rodrigues Alves, nº 95</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/4823-unidades-basicas-de-saude-do-alto-das-oliveiras-e-area-2-atenderao-no-sabado-9-para-vacinacao-contra-a-gripe</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>7</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-08-05 18:56:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://forms.gle/ffvRJRkaCoa87o4X6</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>aqui</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/15099-academia-da-saude-retorna-atividades-e-abre-inscricoes</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>7</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-08-05 19:13:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://chat.whatsapp.com/DthmLwvgFpjKeXjmp1vyDd</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>chat.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>clique aqui</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/13173-psicologos-autonomos-fazem-atendimento-gratuito-a-profissionais-da-linha-de-frente</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>7</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-08-05 19:19:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://www.mdh.gov.br/disque100</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>www.mdh.gov.br</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Disque 100</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/9561-prefeitura-alerta-para-o-dia-da-conscientizacao-contra-violencia-aos-idosos</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>7</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-08-05 19:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>http://www.protejabrasil.com.br/br/</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>www.protejabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Proteja Brasil</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/9561-prefeitura-alerta-para-o-dia-da-conscientizacao-contra-violencia-aos-idosos</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>7</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-08-05 19:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://www.humanizaredes.gov.br/o-que-e/</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>www.humanizaredes.gov.br</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Humaniza Redes – Pacto Nacional de Enfrentamento às Violações de Direitos Humanos</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/9561-prefeitura-alerta-para-o-dia-da-conscientizacao-contra-violencia-aos-idosos</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>7</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-08-05 19:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1ex5D3pPrWsDTSCs02mdam5ACjh8QnP_7s3C1dfsyF6U/edit</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1ex5D3pPrWsDTSCs02mdam5ACjh8QnP_7s3C1dfsyF6U/edit</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/19560-saude-realiza-capacitacao-em-boas-praticas-de-manipulacao-de-alimentos</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>8</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-08-05 20:14:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>http://www.aen.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>www.aen.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>www.aen.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/6112-saude-alerta-para-cuidados-com-a-dengue-durante-as-ferias-escolares</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>8</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-08-05 20:18:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>http://www2.inca.gov.br</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>www2.inca.gov.br</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>http://www2.inca.gov.br</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/5802-centro-da-juventude-recebe-palestra-sobre-outubro-rosa-prevencao-ao-cancer-de-mama</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>8</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-08-05 20:19:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/telemacoborba/inventario_externos.xlsx
+++ b/resultados/telemacoborba/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G217"/>
+  <dimension ref="A1:G219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7897,6 +7897,76 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://www.saude.pr.gov.br/Noticia/Parana-separa-20-mil-doses-para-imunizar-trabalhadores-do-Ensino-Superior</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>www.saude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>matéria da SESA</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/14288-covid-19-saude-comeca-organizar-vacinacao-para-professores-do-ensino-superior</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>8</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:31:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>http://www.mpgo.mp.br/portal/arquivos/2021/03/19/15_35_01_729_Ofi%CC%81cio_Circular_57_2021_SVS_MS.pdf</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>www.mpgo.mp.br</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Ofício na íntegra</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/13540-trabalhadores-de-saude-cadastrados-com-29-anos-ou-mais-podem-se-vacinar-nesta-quinta-22</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>8</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:33:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/telemacoborba/inventario_externos.xlsx
+++ b/resultados/telemacoborba/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +7967,41 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC5-yx6q6pqqUeQJAI-DsTZQ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Canal do YouTube (CLIQUE AQUI).</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/13014-audiencia-publica-de-saude-referente-ao-3-quadrimestre-de-2020-sera-dia-26-2</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>8</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:41:10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/telemacoborba/inventario_externos.xlsx
+++ b/resultados/telemacoborba/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8002,6 +8002,239 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://www.saude.pr.gov.br/Pagina/Sifilis</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>www.saude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://www.saude.pr.gov.br/Pagina/Sifilis</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/18787-saude-realiza-multiplicacao-da-capacitacao-sobre-a-sifilis</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>9</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:06:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pg/PrefeituraTelemacoBorba/photos/?tab=album&amp;album_id=2304729666464199</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/7165-semana-municipal-da-saude-reune-aproximadamente-700-pessoas</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>9</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:06:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>http://www.contadocigarro.org.br</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>www.contadocigarro.org.br</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>www.contadocigarro.org.br</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/7465-acoes-preventivas-em-saude-marcam-o-dia-mundial-sem-tabaco-em-telemaco-borba</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>9</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:09:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/br/app/sesc-paran%C3%A1/id1451489909</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>apps.apple.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/br/app/sesc-paran%C3%A1/id1451489909</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/13500-prefeitura-adere-a-campanha-contra-a-dengue-do-sesc-pr</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>9</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:26:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=br.com.sescpr.app&amp;hl=pt_BR&amp;gl=US</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>play.google.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=br.com.sescpr.app&amp;hl=pt_BR&amp;gl=US</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/13500-prefeitura-adere-a-campanha-contra-a-dengue-do-sesc-pr</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>9</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:26:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pg/PrefeituraTelemacoBorba/photos/?tab=album&amp;album_id=2426100384327126</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/8212-caminhada-abre-a-programacao-do-outubro-rosa-azul</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>10</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-08-07 17:19:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>telemacoborba</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pg/PrefeituraTelemacoBorba/photos/?tab=album&amp;album_id=2480324402238057</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://telemacoborba.pr.gov.br/index.php/imprensa/noticias/saude/8547-campanha-contra-o-aedes-aegypti-segue-ate-14-de-dezembro</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>10</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-08-07 17:23:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
